--- a/Template Pendaftaran Peserta Kolektif.xlsx
+++ b/Template Pendaftaran Peserta Kolektif.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Downloads\yandu-prototype\dokumen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Downloads\yandu-prototype\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D0E1A6-34DB-427F-9B0A-BCF53605C474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BEAE47B-8281-45D4-A869-A5DE84AFE8A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="48">
   <si>
     <t>NRP_NIP</t>
   </si>
@@ -164,6 +164,12 @@
   <si>
     <t>23756669</t>
   </si>
+  <si>
+    <t>PEREMPUAN</t>
+  </si>
+  <si>
+    <t>LAKI-LAKI</t>
+  </si>
 </sst>
 </file>
 
@@ -180,12 +186,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -611,8 +619,8 @@
       <c r="G2" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="15">
-        <v>2</v>
+      <c r="H2" s="15" t="s">
+        <v>46</v>
       </c>
       <c r="I2" s="16" t="s">
         <v>24</v>
@@ -670,8 +678,8 @@
       <c r="G3" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="15">
-        <v>1</v>
+      <c r="H3" s="15" t="s">
+        <v>47</v>
       </c>
       <c r="I3" s="16" t="s">
         <v>34</v>
